--- a/exports/LTF_full_report.xlsx
+++ b/exports/LTF_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.92</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="I2" t="n">
         <v>77.5562600362278</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.31</v>
+        <v>-5</v>
       </c>
       <c r="L2" t="n">
-        <v>3.06</v>
+        <v>5.19</v>
       </c>
       <c r="M2" t="n">
         <v>0.19</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>3.14</v>
       </c>
       <c r="O2" t="n">
         <v>0.5600000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.39</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>76.34999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>76.72059821398794</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.53</v>
+        <v>-1.51</v>
       </c>
       <c r="L3" t="n">
         <v>2.7</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>6.37</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>74.09999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="I4" t="n">
         <v>72.71394239306426</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.89</v>
+        <v>-6.68</v>
       </c>
       <c r="L4" t="n">
-        <v>5.19</v>
+        <v>7.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>4.86</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.38541666666</v>
+        <v>44629.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>64.84999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="I5" t="n">
         <v>64.8923629656508</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>9.869999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="L5" t="n">
         <v>3.82</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>83.65000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I6" t="n">
         <v>81.62091874070629</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55.83333333333334</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>28.59</v>
+        <v>24.83</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>71.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>71.77660602837889</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>65</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>12.07</v>
+        <v>10.22</v>
       </c>
       <c r="L7" t="n">
         <v>3.26</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.4</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>75.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>74.20070472666816</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>3.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>5.21</v>
@@ -897,7 +992,7 @@
         <v>0.76</v>
       </c>
       <c r="N8" t="n">
-        <v>2.71</v>
+        <v>3.19</v>
       </c>
       <c r="O8" t="n">
         <v>2.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="I9" t="n">
         <v>76.98564584602734</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.18</v>
+        <v>-10.63</v>
       </c>
       <c r="L9" t="n">
-        <v>2.86</v>
+        <v>12.87</v>
       </c>
       <c r="M9" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="N9" t="n">
-        <v>1.49</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
         <v>-3.19</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>79.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I10" t="n">
         <v>79.60976685366595</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6</v>
+        <v>-3.08</v>
       </c>
       <c r="L10" t="n">
         <v>7.39</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.99</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>76.95</v>
+        <v>78.5</v>
       </c>
       <c r="I11" t="n">
         <v>78.3117722542202</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>2.22</v>
+        <v>0.25</v>
       </c>
       <c r="L11" t="n">
         <v>2.03</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.96</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>90.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>89.39664676611656</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>76</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>15.03</v>
+        <v>12.87</v>
       </c>
       <c r="L12" t="n">
         <v>5.03</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>88.75</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>89.56832021895129</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.17</v>
+        <v>-1.69</v>
       </c>
       <c r="L13" t="n">
         <v>2.03</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>93.55</v>
+        <v>89</v>
       </c>
       <c r="I14" t="n">
         <v>89.72631205560974</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>3.83</v>
+        <v>-1.22</v>
       </c>
       <c r="L14" t="n">
         <v>4.77</v>
@@ -1239,7 +1406,7 @@
         <v>0.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.32</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
         <v>3.21</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.14</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>92.34999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>92.37441957613828</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.76</v>
+        <v>-4.61</v>
       </c>
       <c r="L15" t="n">
         <v>5.79</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.23</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>89.40929820428764</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.54</v>
+        <v>-4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>3.76</v>
+        <v>4.67</v>
       </c>
       <c r="M16" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="N16" t="n">
         <v>2.28</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>5.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>91.2</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>91.54631347078868</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.36</v>
+        <v>-2.86</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>4.04</v>
       </c>
       <c r="M17" t="n">
-        <v>0.39</v>
+        <v>0.88</v>
       </c>
       <c r="N17" t="n">
         <v>2.56</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.2</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>89.95</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>88.32990414777713</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.85</v>
+        <v>-4.96</v>
       </c>
       <c r="L18" t="n">
-        <v>2.56</v>
+        <v>5.07</v>
       </c>
       <c r="M18" t="n">
         <v>0.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>4.28</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>83.65000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>83.82872231792827</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>3.96</v>
+        <v>3.67</v>
       </c>
       <c r="L19" t="n">
         <v>3.85</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>131.45</v>
+        <v>126.45</v>
       </c>
       <c r="I20" t="n">
         <v>127.1689365553786</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>110.1666666666667</v>
+        <v>111</v>
       </c>
       <c r="K20" t="n">
-        <v>56.67</v>
+        <v>50.72</v>
       </c>
       <c r="L20" t="n">
         <v>0.89</v>
@@ -1581,7 +1820,7 @@
         <v>1.51</v>
       </c>
       <c r="N20" t="n">
-        <v>2.48</v>
+        <v>3.27</v>
       </c>
       <c r="O20" t="n">
         <v>0.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.63</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>123.8</v>
+        <v>124.95</v>
       </c>
       <c r="I21" t="n">
         <v>123.8714431461791</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="L21" t="n">
         <v>6.52</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.83</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45189.38541666666</v>
+        <v>45189.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>127.45</v>
+        <v>125.5</v>
       </c>
       <c r="I22" t="n">
         <v>125.8083480773492</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>0.44</v>
       </c>
       <c r="L22" t="n">
         <v>3.12</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.9</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>127.05</v>
+        <v>132.75</v>
       </c>
       <c r="I23" t="n">
         <v>129.9005781289237</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.24</v>
+        <v>-5.78</v>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>5.82</v>
       </c>
       <c r="M23" t="n">
         <v>0.36</v>
       </c>
       <c r="N23" t="n">
-        <v>2.06</v>
+        <v>4.92</v>
       </c>
       <c r="O23" t="n">
         <v>-1.41</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>149.65</v>
+        <v>141.85</v>
       </c>
       <c r="I24" t="n">
         <v>141.950033661043</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K24" t="n">
-        <v>12.73</v>
+        <v>6.85</v>
       </c>
       <c r="L24" t="n">
         <v>4.63</v>
       </c>
       <c r="M24" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="N24" t="n">
-        <v>5.06</v>
+        <v>5.65</v>
       </c>
       <c r="O24" t="n">
         <v>4.92</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.92</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45260.38541666666</v>
+        <v>45260.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>147</v>
+        <v>148.3</v>
       </c>
       <c r="I25" t="n">
         <v>147.8062603101995</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.63</v>
+        <v>-4.55</v>
       </c>
       <c r="L25" t="n">
-        <v>4.48</v>
+        <v>5.11</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.19</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>156.15</v>
+        <v>149.55</v>
       </c>
       <c r="I26" t="n">
         <v>154.054866208988</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>5.29</v>
+        <v>0.84</v>
       </c>
       <c r="L26" t="n">
         <v>0.88</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>156.2</v>
+        <v>159.95</v>
       </c>
       <c r="I27" t="n">
         <v>158.5656115373263</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.45</v>
+        <v>-6.95</v>
       </c>
       <c r="L27" t="n">
-        <v>4.51</v>
+        <v>7.09</v>
       </c>
       <c r="M27" t="n">
         <v>0.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.16</v>
+        <v>4.23</v>
       </c>
       <c r="O27" t="n">
         <v>-6.3</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45314.55208333334</v>
+        <v>45315.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>161</v>
+        <v>158.5</v>
       </c>
       <c r="I28" t="n">
         <v>160.4965222774168</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="L28" t="n">
         <v>2.16</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>168.5</v>
+        <v>173.35</v>
       </c>
       <c r="I29" t="n">
         <v>172.1820383409931</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.31</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>8.23</v>
+        <v>10.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.18</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.91</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>169.6</v>
+        <v>164.55</v>
       </c>
       <c r="I30" t="n">
         <v>165.7396902090919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.16</v>
+        <v>-5.08</v>
       </c>
       <c r="L30" t="n">
-        <v>4.99</v>
+        <v>5.11</v>
       </c>
       <c r="M30" t="n">
         <v>0.97</v>
       </c>
       <c r="N30" t="n">
-        <v>2.47</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>2.67</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.94</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>167.9</v>
+        <v>174.35</v>
       </c>
       <c r="I31" t="n">
         <v>172.8503836766492</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.04</v>
+        <v>-5.96</v>
       </c>
       <c r="L31" t="n">
-        <v>4.65</v>
+        <v>6.68</v>
       </c>
       <c r="M31" t="n">
-        <v>0.48</v>
+        <v>2.44</v>
       </c>
       <c r="N31" t="n">
-        <v>1.64</v>
+        <v>3.81</v>
       </c>
       <c r="O31" t="n">
         <v>-2.98</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>172.4</v>
+        <v>158.85</v>
       </c>
       <c r="I32" t="n">
         <v>164.5951407697504</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.12</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>1.81</v>
+        <v>11.1</v>
       </c>
       <c r="M32" t="n">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="N32" t="n">
-        <v>1.09</v>
+        <v>7.77</v>
       </c>
       <c r="O32" t="n">
         <v>3.81</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.39</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>156.9</v>
+        <v>159.75</v>
       </c>
       <c r="I33" t="n">
         <v>158.8363197479173</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>1.23</v>
+        <v>-0.57</v>
       </c>
       <c r="L33" t="n">
         <v>7.96</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.93</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>166.15</v>
+        <v>160.65</v>
       </c>
       <c r="I34" t="n">
         <v>163.384767115988</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>4.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>1.88</v>
@@ -2379,7 +2786,7 @@
         <v>2.3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>2.68</v>
       </c>
       <c r="O34" t="n">
         <v>1.4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.68</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.38541666666</v>
+        <v>45450.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>161.9</v>
+        <v>169.35</v>
       </c>
       <c r="I35" t="n">
         <v>163.4577406827327</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.78</v>
+        <v>-5.42</v>
       </c>
       <c r="L35" t="n">
         <v>7.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>178</v>
+        <v>175.29</v>
       </c>
       <c r="I36" t="n">
         <v>177.866783466064</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>5.11</v>
+        <v>3.51</v>
       </c>
       <c r="L36" t="n">
         <v>4.46</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.68</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>169</v>
+        <v>170.63</v>
       </c>
       <c r="I37" t="n">
         <v>170.2717030408759</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>3.59</v>
+        <v>2.66</v>
       </c>
       <c r="L37" t="n">
         <v>4.1</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>4.56</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45541.38541666666</v>
+        <v>45541.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>166.58</v>
+        <v>165.34</v>
       </c>
       <c r="I38" t="n">
         <v>166.2157470631549</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.37</v>
+        <v>-3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>3.07</v>
+        <v>3.43</v>
       </c>
       <c r="M38" t="n">
         <v>0.78</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.97</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45546.55208333334</v>
+        <v>45547.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>167</v>
+        <v>172.66</v>
       </c>
       <c r="I39" t="n">
         <v>172.4369012005089</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-1</v>
+        <v>-4.43</v>
       </c>
       <c r="L39" t="n">
         <v>4.78</v>
@@ -2664,7 +3131,7 @@
         <v>0.86</v>
       </c>
       <c r="N39" t="n">
-        <v>3.54</v>
+        <v>4.31</v>
       </c>
       <c r="O39" t="n">
         <v>-3.06</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>180.84</v>
+        <v>176.59</v>
       </c>
       <c r="I40" t="n">
         <v>179.1329129932532</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>4.74</v>
+        <v>2.28</v>
       </c>
       <c r="L40" t="n">
         <v>2.73</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.42</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>145.49</v>
+        <v>147.94</v>
       </c>
       <c r="I41" t="n">
         <v>145.8906777844491</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K41" t="n">
-        <v>17.61</v>
+        <v>16.22</v>
       </c>
       <c r="L41" t="n">
         <v>3.03</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.75</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>147.15</v>
+        <v>142.83</v>
       </c>
       <c r="I42" t="n">
         <v>143.8359301017493</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.53</v>
+        <v>-3.45</v>
       </c>
       <c r="L42" t="n">
         <v>3.87</v>
@@ -2835,7 +3338,7 @@
         <v>0.82</v>
       </c>
       <c r="N42" t="n">
-        <v>1.59</v>
+        <v>3.74</v>
       </c>
       <c r="O42" t="n">
         <v>1.9</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.76</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>137.65</v>
+        <v>142.55</v>
       </c>
       <c r="I43" t="n">
         <v>141.8667049720479</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>3.63</v>
+        <v>0.2</v>
       </c>
       <c r="L43" t="n">
         <v>3.12</v>
@@ -2892,7 +3407,7 @@
         <v>1.31</v>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>3.77</v>
       </c>
       <c r="O43" t="n">
         <v>-3.74</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.58</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>138.2</v>
+        <v>132.9</v>
       </c>
       <c r="I44" t="n">
         <v>136.4420934229499</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.05</v>
+        <v>-6.77</v>
       </c>
       <c r="L44" t="n">
-        <v>4.16</v>
+        <v>6.94</v>
       </c>
       <c r="M44" t="n">
-        <v>1.04</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="O44" t="n">
         <v>3.77</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.43</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>141.5</v>
+        <v>142.25</v>
       </c>
       <c r="I45" t="n">
         <v>142.0951479398694</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.47</v>
+        <v>-7.04</v>
       </c>
       <c r="L45" t="n">
-        <v>7.11</v>
+        <v>7.55</v>
       </c>
       <c r="M45" t="n">
         <v>0.4</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.56</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>148.27</v>
+        <v>140.51</v>
       </c>
       <c r="I46" t="n">
         <v>143.1243051406997</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>4.23</v>
+        <v>-1.22</v>
       </c>
       <c r="L46" t="n">
         <v>5.66</v>
@@ -3063,7 +3614,7 @@
         <v>2.14</v>
       </c>
       <c r="N46" t="n">
-        <v>3.84</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
         <v>0.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.38</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>141.25</v>
+        <v>143.66</v>
       </c>
       <c r="I47" t="n">
         <v>142.7839795421719</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.53</v>
+        <v>-2.24</v>
       </c>
       <c r="L47" t="n">
         <v>5.16</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>153.69</v>
+        <v>146.35</v>
       </c>
       <c r="I48" t="n">
         <v>149.9961933979311</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>6.98</v>
+        <v>1.87</v>
       </c>
       <c r="L48" t="n">
         <v>4.77</v>
       </c>
       <c r="M48" t="n">
-        <v>1.28</v>
+        <v>8.91</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="O48" t="n">
         <v>-0.79</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>156.7</v>
+        <v>158.54</v>
       </c>
       <c r="I49" t="n">
         <v>157.3835518722059</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.07</v>
+        <v>-8.33</v>
       </c>
       <c r="L49" t="n">
-        <v>7.82</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>2.62</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>7.05</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45772.55208333334</v>
+        <v>45775.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>171.95</v>
+        <v>165.89</v>
       </c>
       <c r="I50" t="n">
         <v>169.1083771920132</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>8.460000000000001</v>
+        <v>4.64</v>
       </c>
       <c r="L50" t="n">
         <v>1.19</v>
       </c>
       <c r="M50" t="n">
-        <v>0.11</v>
+        <v>5.38</v>
       </c>
       <c r="N50" t="n">
         <v>4.14</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.84</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>171.18</v>
+        <v>176.81</v>
       </c>
       <c r="I51" t="n">
         <v>171.834090898078</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.19</v>
+        <v>-6.58</v>
       </c>
       <c r="L51" t="n">
-        <v>4.52</v>
+        <v>6.67</v>
       </c>
       <c r="M51" t="n">
         <v>4.12</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>202.99</v>
+        <v>199.79</v>
       </c>
       <c r="I52" t="n">
         <v>199.9082753056844</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K52" t="n">
-        <v>14.81</v>
+        <v>13</v>
       </c>
       <c r="L52" t="n">
         <v>4.28</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.8</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>203.5</v>
+        <v>211.97</v>
       </c>
       <c r="I53" t="n">
         <v>208.9974549926807</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.86</v>
+        <v>-6.1</v>
       </c>
       <c r="L53" t="n">
-        <v>3.5</v>
+        <v>6.26</v>
       </c>
       <c r="M53" t="n">
         <v>0.76</v>
       </c>
       <c r="N53" t="n">
-        <v>2.01</v>
+        <v>3.88</v>
       </c>
       <c r="O53" t="n">
         <v>-1.72</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45875.55208333334</v>
+        <v>45876.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>201.91</v>
+        <v>197.24</v>
       </c>
       <c r="I54" t="n">
         <v>200.3059891319002</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.75</v>
+        <v>-6.95</v>
       </c>
       <c r="L54" t="n">
-        <v>6.01</v>
+        <v>7.2</v>
       </c>
       <c r="M54" t="n">
         <v>1.07</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.47</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>202.11</v>
+        <v>211.98</v>
       </c>
       <c r="I55" t="n">
         <v>207.0802961290537</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.47</v>
+        <v>-7.47</v>
       </c>
       <c r="L55" t="n">
-        <v>2.84</v>
+        <v>8.42</v>
       </c>
       <c r="M55" t="n">
-        <v>0.45</v>
+        <v>1.38</v>
       </c>
       <c r="N55" t="n">
-        <v>1.67</v>
+        <v>4.34</v>
       </c>
       <c r="O55" t="n">
         <v>-0.37</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.26</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>243.6</v>
+        <v>237.53</v>
       </c>
       <c r="I56" t="n">
         <v>239.1617428357004</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>14.92</v>
+        <v>12.05</v>
       </c>
       <c r="L56" t="n">
         <v>3.64</v>
@@ -3633,7 +4304,7 @@
         <v>0.41</v>
       </c>
       <c r="N56" t="n">
-        <v>2.19</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
         <v>4.34</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.87</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45930.38541666666</v>
+        <v>45930.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>247.32</v>
+        <v>249.3</v>
       </c>
       <c r="I57" t="n">
         <v>248.0032497094007</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.12</v>
+        <v>-4.96</v>
       </c>
       <c r="L57" t="n">
-        <v>4.61</v>
+        <v>5.21</v>
       </c>
       <c r="M57" t="n">
         <v>0.45</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.34</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>300.2</v>
+        <v>297.15</v>
       </c>
       <c r="I58" t="n">
         <v>297.1565585402954</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>79</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>20.42</v>
+        <v>19.19</v>
       </c>
       <c r="L58" t="n">
         <v>0.97</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.97</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46022.38541666666</v>
+        <v>46022.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>313</v>
+        <v>315.9</v>
       </c>
       <c r="I59" t="n">
         <v>313.028163020136</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.33</v>
+        <v>-6.31</v>
       </c>
       <c r="L59" t="n">
-        <v>5.82</v>
+        <v>6.55</v>
       </c>
       <c r="M59" t="n">
         <v>0.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.36</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>313.5</v>
+        <v>308.3</v>
       </c>
       <c r="I60" t="n">
         <v>308.417614575743</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.76</v>
+        <v>-2.41</v>
       </c>
       <c r="L60" t="n">
-        <v>1.52</v>
+        <v>2.99</v>
       </c>
       <c r="M60" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="N60" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="O60" t="n">
         <v>3.74</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46070.55208333334</v>
+        <v>46071.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>297.6</v>
+        <v>298.9</v>
       </c>
       <c r="I61" t="n">
         <v>298.8511580153784</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="L61" t="n">
         <v>1.65</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.32</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46080.38541666666</v>
+        <v>46080.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>291.5</v>
+        <v>279.8</v>
       </c>
       <c r="I62" t="n">
         <v>287.2794389286256</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.48</v>
+        <v>-6.39</v>
       </c>
       <c r="L62" t="n">
         <v>6.99</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>10.49</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>254.49</v>
+        <v>276.6</v>
       </c>
       <c r="I63" t="n">
         <v>260.3726702778894</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>9.050000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="L63" t="n">
         <v>4.47</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>5.31</v>
       </c>
       <c r="N63" t="n">
-        <v>4.85</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O63" t="n">
         <v>-6.55</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.34</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>294.7</v>
+        <v>284.35</v>
       </c>
       <c r="I64" t="n">
         <v>287.3432850375875</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K64" t="n">
-        <v>6.54</v>
+        <v>2.8</v>
       </c>
       <c r="L64" t="n">
         <v>3.76</v>
@@ -4089,7 +4856,7 @@
         <v>1.99</v>
       </c>
       <c r="N64" t="n">
-        <v>2.69</v>
+        <v>4.51</v>
       </c>
       <c r="O64" t="n">
         <v>8.449999999999999</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.42</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>269.4</v>
+        <v>275.75</v>
       </c>
       <c r="I65" t="n">
         <v>272.7353174876334</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>5.26</v>
+        <v>3.02</v>
       </c>
       <c r="L65" t="n">
         <v>3.78</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.57</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>326.4</v>
+        <v>314.75</v>
       </c>
       <c r="I66" t="n">
         <v>316.8793943417662</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K66" t="n">
-        <v>18.37</v>
+        <v>14.14</v>
       </c>
       <c r="L66" t="n">
         <v>2.41</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>311</v>
+        <v>319.85</v>
       </c>
       <c r="I67" t="n">
         <v>317.9159495938255</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>1.19</v>
+        <v>-1.62</v>
       </c>
       <c r="L67" t="n">
         <v>5.96</v>
       </c>
       <c r="M67" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="N67" t="n">
         <v>3.39</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.32</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>309.4</v>
+        <v>306.5</v>
       </c>
       <c r="I68" t="n">
         <v>307.3373240502838</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.27</v>
+        <v>-4.17</v>
       </c>
       <c r="L68" t="n">
-        <v>4.8</v>
+        <v>5.36</v>
       </c>
       <c r="M68" t="n">
         <v>0.64</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.28</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46283.38541666666</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>308.15</v>
+        <v>312.35</v>
       </c>
       <c r="I69" t="n">
         <v>311.5951194666004</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.54</v>
+        <v>-1.91</v>
       </c>
       <c r="L69" t="n">
         <v>4.57</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.72</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>310.15</v>
+        <v>284</v>
       </c>
       <c r="I70" t="n">
         <v>294.4860096179635</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.7</v>
+        <v>-9.08</v>
       </c>
       <c r="L70" t="n">
-        <v>3.3</v>
+        <v>10.68</v>
       </c>
       <c r="M70" t="n">
-        <v>0.43</v>
+        <v>10.04</v>
       </c>
       <c r="N70" t="n">
-        <v>1.65</v>
+        <v>8.92</v>
       </c>
       <c r="O70" t="n">
         <v>3.36</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>44</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.15</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.78</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.45</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.67</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.8</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.05</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.87</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.23</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.48</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.48</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="27">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
